--- a/data/lexicon.xlsx
+++ b/data/lexicon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>meaning</t>
   </si>
@@ -54,6 +54,60 @@
   </si>
   <si>
     <t>ফজোরত | বেইন্নে</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all </t>
+  </si>
+  <si>
+    <t>সবাই</t>
+  </si>
+  <si>
+    <t>বিয়াজ্ঞুন | বেজ্ঞুন</t>
+  </si>
+  <si>
+    <t>coming</t>
+  </si>
+  <si>
+    <t>আসছি</t>
+  </si>
+  <si>
+    <t>আইর | আইয়্যির</t>
+  </si>
+  <si>
+    <t>tomorrow</t>
+  </si>
+  <si>
+    <t>আগামিকাল</t>
+  </si>
+  <si>
+    <t>হালিইয়্যে | হালোয়া | হালিয়ে</t>
+  </si>
+  <si>
+    <t>today</t>
+  </si>
+  <si>
+    <t>আজকে</t>
+  </si>
+  <si>
+    <t>আজিয়ে | আজিইয়্যে | আজুয়া</t>
+  </si>
+  <si>
+    <t>yesterday</t>
+  </si>
+  <si>
+    <t>গতকাল</t>
+  </si>
+  <si>
+    <t>গত হালিয়ে | গত হালিইয়্যে | গত হালোয়া</t>
+  </si>
+  <si>
+    <t>to come</t>
+  </si>
+  <si>
+    <t>আসতে</t>
+  </si>
+  <si>
+    <t>আইতে | আইসতে</t>
   </si>
 </sst>
 </file>
@@ -675,12 +729,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1236,111 +1287,147 @@
       </c>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" ht="25" customHeight="1" spans="1:3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
     </row>
     <row r="16" ht="25" customHeight="1" spans="1:3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
     </row>
     <row r="17" ht="25" customHeight="1" spans="1:3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
     </row>
     <row r="18" ht="25" customHeight="1" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
     </row>
     <row r="19" ht="25" customHeight="1" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
     </row>
     <row r="20" ht="25" customHeight="1" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/lexicon.xlsx
+++ b/data/lexicon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>meaning</t>
   </si>
@@ -47,7 +47,7 @@
     <t>ভালা | গম</t>
   </si>
   <si>
-    <t>In the morning</t>
+    <t>In_the_morning</t>
   </si>
   <si>
     <t>সকালে</t>
@@ -101,13 +101,40 @@
     <t>গত হালিয়ে | গত হালিইয়্যে | গত হালোয়া</t>
   </si>
   <si>
-    <t>to come</t>
+    <t>to_come</t>
   </si>
   <si>
     <t>আসতে</t>
   </si>
   <si>
     <t>আইতে | আইসতে</t>
+  </si>
+  <si>
+    <t>so_much</t>
+  </si>
+  <si>
+    <t>এত</t>
+  </si>
+  <si>
+    <t>এতো | এল্লেত</t>
+  </si>
+  <si>
+    <t>at_noon</t>
+  </si>
+  <si>
+    <t>দুপুরে</t>
+  </si>
+  <si>
+    <t>দুইরগে | দুইজ্জে</t>
+  </si>
+  <si>
+    <t>it_seems</t>
+  </si>
+  <si>
+    <t>লাগতাছে | লাগছে</t>
+  </si>
+  <si>
+    <t>লাগের | লার</t>
   </si>
 </sst>
 </file>
@@ -1375,19 +1402,37 @@
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:3">
       <c r="A13" s="1"/>

--- a/data/lexicon.xlsx
+++ b/data/lexicon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>meaning</t>
   </si>
@@ -135,6 +135,87 @@
   </si>
   <si>
     <t>লাগের | লার</t>
+  </si>
+  <si>
+    <t>a_little</t>
+  </si>
+  <si>
+    <t>একটু</t>
+  </si>
+  <si>
+    <t>এক্কানা | ইক্কিনি</t>
+  </si>
+  <si>
+    <t>otherwise</t>
+  </si>
+  <si>
+    <t>না হয়</t>
+  </si>
+  <si>
+    <t>নয়তো | নইলি</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ask </t>
+  </si>
+  <si>
+    <t>জিজ্ঞেস</t>
+  </si>
+  <si>
+    <t>ফুসর | ফুস</t>
+  </si>
+  <si>
+    <t>listen</t>
+  </si>
+  <si>
+    <t>শুনো</t>
+  </si>
+  <si>
+    <t>উনো | ফুনো</t>
+  </si>
+  <si>
+    <t>know</t>
+  </si>
+  <si>
+    <t>জান</t>
+  </si>
+  <si>
+    <t>জানো | হইত পারো</t>
+  </si>
+  <si>
+    <t>i_know</t>
+  </si>
+  <si>
+    <t>জানি</t>
+  </si>
+  <si>
+    <t>জানি | হইত পারি</t>
+  </si>
+  <si>
+    <t>don't_know</t>
+  </si>
+  <si>
+    <t>জানিনা</t>
+  </si>
+  <si>
+    <t>ন জানি | হইত ন পারি</t>
+  </si>
+  <si>
+    <t>with</t>
+  </si>
+  <si>
+    <t>সাথে</t>
+  </si>
+  <si>
+    <t>লগে | ওয়ারে | ফুয়ারে</t>
+  </si>
+  <si>
+    <t>work</t>
+  </si>
+  <si>
+    <t>কাজ</t>
+  </si>
+  <si>
+    <t>হাজ | হাম</t>
   </si>
 </sst>
 </file>
@@ -1296,7 +1377,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="40.7777777777778" customWidth="1"/>
@@ -1435,44 +1516,248 @@
       </c>
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
+      <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
+      <c r="A15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="16" ht="25" customHeight="1" spans="1:3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
+      <c r="A16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="17" ht="25" customHeight="1" spans="1:3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="A17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="18" ht="25" customHeight="1" spans="1:3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
+      <c r="A18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="19" ht="25" customHeight="1" spans="1:3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
+      <c r="A19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="20" ht="25" customHeight="1" spans="1:3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
+      <c r="A20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" ht="16.2" spans="1:3">
+      <c r="A21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" ht="16.2" spans="1:3">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23" ht="16.2" spans="1:3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" ht="16.2" spans="1:3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" ht="16.2" spans="1:3">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+    </row>
+    <row r="26" ht="16.2" spans="1:3">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+    </row>
+    <row r="27" ht="16.2" spans="1:3">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+    </row>
+    <row r="28" ht="16.2" spans="1:3">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+    </row>
+    <row r="29" ht="16.2" spans="1:3">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+    </row>
+    <row r="30" ht="16.2" spans="1:3">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+    </row>
+    <row r="31" ht="16.2" spans="1:3">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+    </row>
+    <row r="32" ht="16.2" spans="1:3">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+    </row>
+    <row r="33" ht="16.2" spans="1:3">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+    </row>
+    <row r="34" ht="16.2" spans="1:3">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+    </row>
+    <row r="35" ht="16.2" spans="1:3">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+    </row>
+    <row r="36" ht="16.2" spans="1:3">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+    </row>
+    <row r="37" ht="16.2" spans="1:3">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+    </row>
+    <row r="38" ht="16.2" spans="1:3">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+    </row>
+    <row r="39" ht="16.2" spans="1:3">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+    </row>
+    <row r="40" ht="16.2" spans="1:3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+    </row>
+    <row r="41" ht="16.2" spans="1:3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+    </row>
+    <row r="42" ht="16.2" spans="1:3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+    </row>
+    <row r="43" ht="16.2" spans="1:3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+    </row>
+    <row r="44" ht="16.2" spans="1:3">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+    </row>
+    <row r="45" ht="16.2" spans="1:3">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+    </row>
+    <row r="46" ht="16.2" spans="1:3">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+    </row>
+    <row r="47" ht="16.2" spans="1:3">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+    </row>
+    <row r="48" ht="16.2" spans="1:3">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+    </row>
+    <row r="49" ht="16.2" spans="1:3">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+    </row>
+    <row r="50" ht="16.2" spans="1:3">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/lexicon.xlsx
+++ b/data/lexicon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t>meaning</t>
   </si>
@@ -41,7 +41,7 @@
     <t>good</t>
   </si>
   <si>
-    <t>ভালো</t>
+    <t>ভালো | ভাল</t>
   </si>
   <si>
     <t>ভালা | গম</t>
@@ -216,6 +216,51 @@
   </si>
   <si>
     <t>হাজ | হাম</t>
+  </si>
+  <si>
+    <t>tomato</t>
+  </si>
+  <si>
+    <t>টমেটো</t>
+  </si>
+  <si>
+    <t>টমেটু | হাট্টা বেইয়্যুন | হরো বেইয়্যুন</t>
+  </si>
+  <si>
+    <t>bharta</t>
+  </si>
+  <si>
+    <t>ভর্তা</t>
+  </si>
+  <si>
+    <t>ভত্তা | চান্নি</t>
+  </si>
+  <si>
+    <t>quickly</t>
+  </si>
+  <si>
+    <t>জলদি | তাড়াতাড়ি</t>
+  </si>
+  <si>
+    <t>তারাতারি | হারা</t>
+  </si>
+  <si>
+    <t>together</t>
+  </si>
+  <si>
+    <t>একসাথে</t>
+  </si>
+  <si>
+    <t>এক্কোত্তরে | এক্কোওয়ারে | একলগে | এক্কোফুয়ারে</t>
+  </si>
+  <si>
+    <t>like_this</t>
+  </si>
+  <si>
+    <t>এভাবে</t>
+  </si>
+  <si>
+    <t>এল্লেত | এন গরি</t>
   </si>
 </sst>
 </file>
@@ -1615,29 +1660,59 @@
       </c>
     </row>
     <row r="22" ht="16.2" spans="1:3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
+      <c r="A22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="23" ht="16.2" spans="1:3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
+      <c r="A23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="24" ht="16.2" spans="1:3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
+      <c r="A24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="25" ht="16.2" spans="1:3">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
+      <c r="A25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="26" ht="16.2" spans="1:3">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
+      <c r="A26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="27" ht="16.2" spans="1:3">
       <c r="A27" s="1"/>

--- a/data/lexicon.xlsx
+++ b/data/lexicon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t>meaning</t>
   </si>
@@ -242,7 +242,7 @@
     <t>জলদি | তাড়াতাড়ি</t>
   </si>
   <si>
-    <t>তারাতারি | হারা</t>
+    <t>তারাতারি | হারা | জলদি</t>
   </si>
   <si>
     <t>together</t>
@@ -261,6 +261,15 @@
   </si>
   <si>
     <t>এল্লেত | এন গরি</t>
+  </si>
+  <si>
+    <t>tired</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ক্লান্ত </t>
+  </si>
+  <si>
+    <t>হয়রান | অরান</t>
   </si>
 </sst>
 </file>
@@ -1715,9 +1724,15 @@
       </c>
     </row>
     <row r="27" ht="16.2" spans="1:3">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
+      <c r="A27" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="28" ht="16.2" spans="1:3">
       <c r="A28" s="1"/>

--- a/data/lexicon.xlsx
+++ b/data/lexicon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t>meaning</t>
   </si>
@@ -270,6 +270,15 @@
   </si>
   <si>
     <t>হয়রান | অরান</t>
+  </si>
+  <si>
+    <t>outside</t>
+  </si>
+  <si>
+    <t>বাইরে</t>
+  </si>
+  <si>
+    <t>বাইরে | বাদ্দি</t>
   </si>
 </sst>
 </file>
@@ -1735,9 +1744,15 @@
       </c>
     </row>
     <row r="28" ht="16.2" spans="1:3">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
+      <c r="A28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="29" ht="16.2" spans="1:3">
       <c r="A29" s="1"/>

--- a/data/lexicon.xlsx
+++ b/data/lexicon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
   <si>
     <t>meaning</t>
   </si>
@@ -279,6 +279,24 @@
   </si>
   <si>
     <t>বাইরে | বাদ্দি</t>
+  </si>
+  <si>
+    <t>blind</t>
+  </si>
+  <si>
+    <t>কানা | অন্ধ</t>
+  </si>
+  <si>
+    <t>আন্ধা | আধা | হানা</t>
+  </si>
+  <si>
+    <t>dirty</t>
+  </si>
+  <si>
+    <t>ময়লা</t>
+  </si>
+  <si>
+    <t>হাচারা | ময়লা</t>
   </si>
 </sst>
 </file>
@@ -1755,14 +1773,26 @@
       </c>
     </row>
     <row r="29" ht="16.2" spans="1:3">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
+      <c r="A29" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="30" ht="16.2" spans="1:3">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
+      <c r="A30" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="31" ht="16.2" spans="1:3">
       <c r="A31" s="1"/>

--- a/data/lexicon.xlsx
+++ b/data/lexicon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>meaning</t>
   </si>
@@ -248,7 +248,7 @@
     <t>together</t>
   </si>
   <si>
-    <t>একসাথে</t>
+    <t>একসাথে | একসঙ্গে</t>
   </si>
   <si>
     <t>এক্কোত্তরে | এক্কোওয়ারে | একলগে | এক্কোফুয়ারে</t>
@@ -297,6 +297,15 @@
   </si>
   <si>
     <t>হাচারা | ময়লা</t>
+  </si>
+  <si>
+    <t>insect</t>
+  </si>
+  <si>
+    <t>পোকা</t>
+  </si>
+  <si>
+    <t>ফুক | ফুগ</t>
   </si>
 </sst>
 </file>
@@ -1795,9 +1804,15 @@
       </c>
     </row>
     <row r="31" ht="16.2" spans="1:3">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
+      <c r="A31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="32" ht="16.2" spans="1:3">
       <c r="A32" s="1"/>

--- a/data/lexicon.xlsx
+++ b/data/lexicon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
   <si>
     <t>meaning</t>
   </si>
@@ -306,6 +306,51 @@
   </si>
   <si>
     <t>ফুক | ফুগ</t>
+  </si>
+  <si>
+    <t>dishes</t>
+  </si>
+  <si>
+    <t>থালাবসন</t>
+  </si>
+  <si>
+    <t>বাসনহুটারা | থালবাসোন</t>
+  </si>
+  <si>
+    <t>kitchen</t>
+  </si>
+  <si>
+    <t>রান্নাঘর</t>
+  </si>
+  <si>
+    <t>বসহানা | পাকঘর | রান্নাঘর</t>
+  </si>
+  <si>
+    <t>yet</t>
+  </si>
+  <si>
+    <t>এখনো</t>
+  </si>
+  <si>
+    <t>এইজু | এহনো</t>
+  </si>
+  <si>
+    <t>all_day</t>
+  </si>
+  <si>
+    <t>সারাদিন</t>
+  </si>
+  <si>
+    <t>পুরোদিন | আরাদিন</t>
+  </si>
+  <si>
+    <t>clean</t>
+  </si>
+  <si>
+    <t>পরিষ্কার</t>
+  </si>
+  <si>
+    <t>সাফ | পরিষ্কার</t>
   </si>
 </sst>
 </file>
@@ -1815,29 +1860,59 @@
       </c>
     </row>
     <row r="32" ht="16.2" spans="1:3">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
+      <c r="A32" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="33" ht="16.2" spans="1:3">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
+      <c r="A33" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="34" ht="16.2" spans="1:3">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
+      <c r="A34" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="35" ht="16.2" spans="1:3">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
+      <c r="A35" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="36" ht="16.2" spans="1:3">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
+      <c r="A36" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="37" ht="16.2" spans="1:3">
       <c r="A37" s="1"/>

--- a/data/lexicon.xlsx
+++ b/data/lexicon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
   <si>
     <t>meaning</t>
   </si>
@@ -351,6 +351,24 @@
   </si>
   <si>
     <t>সাফ | পরিষ্কার</t>
+  </si>
+  <si>
+    <t>guest</t>
+  </si>
+  <si>
+    <t>মেহমান</t>
+  </si>
+  <si>
+    <t>গরবা | মেমান</t>
+  </si>
+  <si>
+    <t>where</t>
+  </si>
+  <si>
+    <t>কোথায়</t>
+  </si>
+  <si>
+    <t>হনডে | হডে</t>
   </si>
 </sst>
 </file>
@@ -1915,14 +1933,26 @@
       </c>
     </row>
     <row r="37" ht="16.2" spans="1:3">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
+      <c r="A37" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="38" ht="16.2" spans="1:3">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
+      <c r="A38" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="39" ht="16.2" spans="1:3">
       <c r="A39" s="1"/>

--- a/data/lexicon.xlsx
+++ b/data/lexicon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
   <si>
     <t>meaning</t>
   </si>
@@ -369,6 +369,15 @@
   </si>
   <si>
     <t>হনডে | হডে</t>
+  </si>
+  <si>
+    <t>shoal_fish</t>
+  </si>
+  <si>
+    <t>শোল মাছ</t>
+  </si>
+  <si>
+    <t>অলি মাছ | অইল মাছ</t>
   </si>
 </sst>
 </file>
@@ -1955,9 +1964,15 @@
       </c>
     </row>
     <row r="39" ht="16.2" spans="1:3">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
+      <c r="A39" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="40" ht="16.2" spans="1:3">
       <c r="A40" s="1"/>

--- a/data/lexicon.xlsx
+++ b/data/lexicon.xlsx
@@ -239,7 +239,7 @@
     <t>quickly</t>
   </si>
   <si>
-    <t>জলদি | তাড়াতাড়ি</t>
+    <t>জলদি | তাড়াতাড়ি | দ্রুত</t>
   </si>
   <si>
     <t>তারাতারি | হারা | জলদি</t>
@@ -1019,7 +1019,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>

--- a/data/lexicon.xlsx
+++ b/data/lexicon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
   <si>
     <t>meaning</t>
   </si>
@@ -378,6 +378,24 @@
   </si>
   <si>
     <t>অলি মাছ | অইল মাছ</t>
+  </si>
+  <si>
+    <t>beside</t>
+  </si>
+  <si>
+    <t>পাশে</t>
+  </si>
+  <si>
+    <t>পাশে | ডাহে</t>
+  </si>
+  <si>
+    <t>only</t>
+  </si>
+  <si>
+    <t>শুধু</t>
+  </si>
+  <si>
+    <t>উদো | শুধু</t>
   </si>
 </sst>
 </file>
@@ -1975,14 +1993,26 @@
       </c>
     </row>
     <row r="40" ht="16.2" spans="1:3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
+      <c r="A40" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="41" ht="16.2" spans="1:3">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
+      <c r="A41" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="42" ht="16.2" spans="1:3">
       <c r="A42" s="1"/>

--- a/data/lexicon.xlsx
+++ b/data/lexicon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
   <si>
     <t>meaning</t>
   </si>
@@ -396,6 +396,24 @@
   </si>
   <si>
     <t>উদো | শুধু</t>
+  </si>
+  <si>
+    <t>up</t>
+  </si>
+  <si>
+    <t>উপরে</t>
+  </si>
+  <si>
+    <t>উদ্দি | উরে</t>
+  </si>
+  <si>
+    <t>to_keep</t>
+  </si>
+  <si>
+    <t>রাখতে</t>
+  </si>
+  <si>
+    <t>রাইখতে | রাহিতে</t>
   </si>
 </sst>
 </file>
@@ -2015,14 +2033,26 @@
       </c>
     </row>
     <row r="42" ht="16.2" spans="1:3">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
+      <c r="A42" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="43" ht="16.2" spans="1:3">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
+      <c r="A43" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="44" ht="16.2" spans="1:3">
       <c r="A44" s="1"/>

--- a/data/lexicon.xlsx
+++ b/data/lexicon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t>meaning</t>
   </si>
@@ -414,6 +414,15 @@
   </si>
   <si>
     <t>রাইখতে | রাহিতে</t>
+  </si>
+  <si>
+    <t>light</t>
+  </si>
+  <si>
+    <t>হালকা</t>
+  </si>
+  <si>
+    <t>হালকা | আলহা</t>
   </si>
 </sst>
 </file>
@@ -2055,9 +2064,15 @@
       </c>
     </row>
     <row r="44" ht="16.2" spans="1:3">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
+      <c r="A44" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="45" ht="16.2" spans="1:3">
       <c r="A45" s="1"/>

--- a/data/lexicon.xlsx
+++ b/data/lexicon.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t>meaning</t>
   </si>
@@ -176,7 +176,7 @@
     <t>know</t>
   </si>
   <si>
-    <t>জান</t>
+    <t>জানো</t>
   </si>
   <si>
     <t>জানো | হইত পারো</t>
@@ -341,7 +341,7 @@
     <t>সারাদিন</t>
   </si>
   <si>
-    <t>পুরোদিন | আরাদিন</t>
+    <t>ফুরোদিন | আরাদিন</t>
   </si>
   <si>
     <t>clean</t>
@@ -423,6 +423,15 @@
   </si>
   <si>
     <t>হালকা | আলহা</t>
+  </si>
+  <si>
+    <t>talk</t>
+  </si>
+  <si>
+    <t>কথা</t>
+  </si>
+  <si>
+    <t>হতা | হথা</t>
   </si>
 </sst>
 </file>
@@ -2075,9 +2084,15 @@
       </c>
     </row>
     <row r="45" ht="16.2" spans="1:3">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
+      <c r="A45" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="46" ht="16.2" spans="1:3">
       <c r="A46" s="1"/>
